--- a/ig/DM-MARS-2026/ASS-A14-FamilleActivite-ActiviteOperationnelle.xlsx
+++ b/ig/DM-MARS-2026/ASS-A14-FamilleActivite-ActiviteOperationnelle.xlsx
@@ -106,7 +106,7 @@
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R211-ActiviteOperationnelle/FHIR/TRE-R211-ActiviteOperationnelle|20251222120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R211-ActiviteOperationnelle/FHIR/TRE-R211-ActiviteOperationnelle|20260330120000</t>
   </si>
   <si>
     <t>2.1.1.1</t>
